--- a/artfynd/A 47408-2024 artfynd.xlsx
+++ b/artfynd/A 47408-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122505603</v>
+        <v>122504872</v>
       </c>
       <c r="B2" t="n">
-        <v>98202</v>
+        <v>90833</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,33 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>5442</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -758,7 +756,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,12 +766,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Min. 36 ex.</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,7 +786,17 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Barrdominerat, lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′02.6″N, 15°29′17.2″E</t>
+          <t>Barrdominerat, lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′03.7″N, 15°29′16.5″E</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Pinus</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -811,10 +814,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122504872</v>
+        <v>122505603</v>
       </c>
       <c r="B3" t="n">
-        <v>90828</v>
+        <v>98211</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,38 +826,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -897,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -907,7 +902,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Min. 36 ex.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,22 +927,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Barrdominerat, lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′03.7″N, 15°29′16.5″E</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tallar</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Pinus</t>
+          <t>Barrdominerat, lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′02.6″N, 15°29′17.2″E</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 47408-2024 artfynd.xlsx
+++ b/artfynd/A 47408-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122504872</v>
+        <v>122505603</v>
       </c>
       <c r="B2" t="n">
-        <v>90833</v>
+        <v>98224</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,33 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>220787</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -756,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -766,7 +768,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Min. 36 ex.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,17 +793,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Barrdominerat, lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′03.7″N, 15°29′16.5″E</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Pinus</t>
+          <t>Barrdominerat, lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′02.6″N, 15°29′17.2″E</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -814,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122505603</v>
+        <v>122504872</v>
       </c>
       <c r="B3" t="n">
-        <v>98211</v>
+        <v>90846</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,30 +823,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5442</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -892,7 +897,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,12 +907,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Min. 36 ex.</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,7 +927,22 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Barrdominerat, lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′02.6″N, 15°29′17.2″E</t>
+          <t>Barrdominerat, lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′03.7″N, 15°29′16.5″E</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tallar</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Pinus</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 47408-2024 artfynd.xlsx
+++ b/artfynd/A 47408-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122505603</v>
       </c>
       <c r="B2" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>122504872</v>
       </c>
       <c r="B3" t="n">
-        <v>90846</v>
+        <v>90859</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 47408-2024 artfynd.xlsx
+++ b/artfynd/A 47408-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122505603</v>
+        <v>122504872</v>
       </c>
       <c r="B2" t="n">
-        <v>98237</v>
+        <v>90853</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -758,7 +761,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,12 +771,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Min. 36 ex.</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,7 +791,22 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Barrdominerat, lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′02.6″N, 15°29′17.2″E</t>
+          <t>Barrdominerat, lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′03.7″N, 15°29′16.5″E</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tallar</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Pinus</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -811,10 +824,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122504872</v>
+        <v>122505603</v>
       </c>
       <c r="B3" t="n">
-        <v>90859</v>
+        <v>98240</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,38 +836,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -897,7 +907,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -907,7 +917,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Min. 36 ex.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,22 +942,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Barrdominerat, lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′03.7″N, 15°29′16.5″E</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tallar</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Pinus</t>
+          <t>Barrdominerat, lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′02.6″N, 15°29′17.2″E</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 47408-2024 artfynd.xlsx
+++ b/artfynd/A 47408-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122504872</v>
+        <v>122505603</v>
       </c>
       <c r="B2" t="n">
-        <v>90853</v>
+        <v>98240</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -761,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -771,7 +768,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Min. 36 ex.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,22 +793,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Barrdominerat, lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′03.7″N, 15°29′16.5″E</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tallar</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Pinus</t>
+          <t>Barrdominerat, lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′02.6″N, 15°29′17.2″E</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -824,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122505603</v>
+        <v>122504872</v>
       </c>
       <c r="B3" t="n">
-        <v>98240</v>
+        <v>90853</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -836,35 +823,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -907,7 +897,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -917,12 +907,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Min. 36 ex.</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -942,7 +927,22 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Barrdominerat, lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′02.6″N, 15°29′17.2″E</t>
+          <t>Barrdominerat, lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′03.7″N, 15°29′16.5″E</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tallar</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Pinus</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 47408-2024 artfynd.xlsx
+++ b/artfynd/A 47408-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122505603</v>
+        <v>122504872</v>
       </c>
       <c r="B2" t="n">
-        <v>98240</v>
+        <v>90854</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -758,7 +761,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,12 +771,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Min. 36 ex.</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,7 +791,22 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Barrdominerat, lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′02.6″N, 15°29′17.2″E</t>
+          <t>Barrdominerat, lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′03.7″N, 15°29′16.5″E</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tallar</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Pinus</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -811,10 +824,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122504872</v>
+        <v>122505603</v>
       </c>
       <c r="B3" t="n">
-        <v>90853</v>
+        <v>98241</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,38 +836,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -897,7 +907,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -907,7 +917,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Min. 36 ex.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,22 +942,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Barrdominerat, lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′03.7″N, 15°29′16.5″E</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tallar</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Pinus</t>
+          <t>Barrdominerat, lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′02.6″N, 15°29′17.2″E</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 47408-2024 artfynd.xlsx
+++ b/artfynd/A 47408-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122504872</v>
       </c>
       <c r="B2" t="n">
-        <v>90854</v>
+        <v>90857</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>122505603</v>
       </c>
       <c r="B3" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 47408-2024 artfynd.xlsx
+++ b/artfynd/A 47408-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -958,6 +958,605 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122734520</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98244</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Vallsnäs skog 0-12, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>528584</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6454953</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Min. 32 rosetter, varav 1 ex blomknopp.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.9″N, 15°29′12.4″E</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122730998</v>
+      </c>
+      <c r="B5" t="n">
+        <v>8430</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vallsnäs skog 0-11, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>528638</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6454971</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>*kläck</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′05.4″N, 15°29′14.9″E</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Betula</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122732619</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57400</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vallsnäs skog 0-11, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>528638</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6454971</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier.</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tallar</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Mkt grov ved. # Pinus</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122730225</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5173</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Vallsnäs skog 0-12, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>528584</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6454953</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier.</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>granar</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Delvis markkontakt. Fuktig miljö. # Picea</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47408-2024 artfynd.xlsx
+++ b/artfynd/A 47408-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1557,6 +1557,435 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122757058</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98345</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Vallsnäs skog0-1, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>528577</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6454845</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Min. 13 ex.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker:  58°14′02.9″N, 15°29′11″E</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122752963</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98345</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Vallsnäs skog 0-13, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>528514</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6454919</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>3 ex</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′05.4″N, 15°29′09.1″E</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122758132</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8430</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Vallsnäs skog 0-12, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>528584</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6454953</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>*kläck/luft</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.1″N, 15°29′11.2″E</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Betula</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47408-2024 artfynd.xlsx
+++ b/artfynd/A 47408-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1257,10 +1257,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122732619</v>
+        <v>122730225</v>
       </c>
       <c r="B6" t="n">
-        <v>57400</v>
+        <v>5173</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1269,46 +1269,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-11, Ög</t>
+          <t>Vallsnäs skog 0-12, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528638</v>
+        <v>528584</v>
       </c>
       <c r="R6" t="n">
-        <v>6454971</v>
+        <v>6454953</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1340,7 +1341,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1350,7 +1351,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1359,6 +1360,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1374,22 +1376,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>tallar</t>
+          <t>granar</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Pinus</t>
+          <t>Picea</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Mkt grov ved. # Pinus</t>
+          <t>Horizontal, dead without ground contact # Delvis markkontakt. Fuktig miljö. # Picea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1407,10 +1409,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122730225</v>
+        <v>122732619</v>
       </c>
       <c r="B7" t="n">
-        <v>5173</v>
+        <v>57400</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1419,47 +1421,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-12, Ög</t>
+          <t>Vallsnäs skog 0-11, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528584</v>
+        <v>528638</v>
       </c>
       <c r="R7" t="n">
-        <v>6454953</v>
+        <v>6454971</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1491,7 +1492,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1501,7 +1502,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1510,7 +1511,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1526,22 +1526,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>granar</t>
+          <t>tallar</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea</t>
+          <t>Pinus</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Delvis markkontakt. Fuktig miljö. # Picea</t>
+          <t>Standing dead tree/snags # Mkt grov ved. # Pinus</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1986,6 +1986,163 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122754716</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5173</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Vallsnäs skog 0-13, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>528514</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6454919</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>*gnag/kläck</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier.</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>tallar</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Pinus</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47408-2024 artfynd.xlsx
+++ b/artfynd/A 47408-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1257,10 +1257,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122730225</v>
+        <v>122732619</v>
       </c>
       <c r="B6" t="n">
-        <v>5173</v>
+        <v>57400</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1269,47 +1269,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-12, Ög</t>
+          <t>Vallsnäs skog 0-11, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528584</v>
+        <v>528638</v>
       </c>
       <c r="R6" t="n">
-        <v>6454953</v>
+        <v>6454971</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1341,7 +1340,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1351,7 +1350,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1360,7 +1359,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1376,22 +1374,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>granar</t>
+          <t>tallar</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea</t>
+          <t>Pinus</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Delvis markkontakt. Fuktig miljö. # Picea</t>
+          <t>Standing dead tree/snags # Mkt grov ved. # Pinus</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1409,10 +1407,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122732619</v>
+        <v>122757058</v>
       </c>
       <c r="B7" t="n">
-        <v>57400</v>
+        <v>98345</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1421,46 +1419,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-11, Ög</t>
+          <t>Vallsnäs skog0-1, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528638</v>
+        <v>528577</v>
       </c>
       <c r="R7" t="n">
-        <v>6454971</v>
+        <v>6454845</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1487,22 +1485,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Min. 13 ex.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1511,6 +1514,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1521,27 +1525,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier.</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>tallar</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Pinus</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Mkt grov ved. # Pinus</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker:  58°14′02.9″N, 15°29′11″E</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1559,7 +1543,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122757058</v>
+        <v>122752963</v>
       </c>
       <c r="B8" t="n">
         <v>98345</v>
@@ -1594,7 +1578,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -1603,14 +1587,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vallsnäs skog0-1, Ög</t>
+          <t>Vallsnäs skog 0-13, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528577</v>
+        <v>528514</v>
       </c>
       <c r="R8" t="n">
-        <v>6454845</v>
+        <v>6454919</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1642,7 +1626,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1652,12 +1636,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Min. 13 ex.</t>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1677,7 +1661,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker:  58°14′02.9″N, 15°29′11″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′05.4″N, 15°29′09.1″E</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1695,10 +1679,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122752963</v>
+        <v>122758132</v>
       </c>
       <c r="B9" t="n">
-        <v>98345</v>
+        <v>8430</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1707,46 +1691,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-13, Ög</t>
+          <t>Vallsnäs skog 0-12, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528514</v>
+        <v>528584</v>
       </c>
       <c r="R9" t="n">
-        <v>6454919</v>
+        <v>6454953</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1778,7 +1763,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1788,12 +1773,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>3 ex</t>
+          <t>*kläck/luft</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1813,7 +1798,27 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′05.4″N, 15°29′09.1″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.1″N, 15°29′11.2″E</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Betula</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1831,10 +1836,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122758132</v>
+        <v>122788467</v>
       </c>
       <c r="B10" t="n">
-        <v>8430</v>
+        <v>98347</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1843,47 +1848,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-12, Ög</t>
+          <t>Vallsnäs skog 0-11, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528584</v>
+        <v>528638</v>
       </c>
       <c r="R10" t="n">
-        <v>6454953</v>
+        <v>6454971</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1910,27 +1914,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>*kläck/luft</t>
+          <t>5 ex.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1950,27 +1954,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.1″N, 15°29′11.2″E</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Betula</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′06.3″N, 15°29′15.3″E</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1988,7 +1972,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122754716</v>
+        <v>122730225</v>
       </c>
       <c r="B11" t="n">
         <v>5173</v>
@@ -2033,14 +2017,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-13, Ög</t>
+          <t>Vallsnäs skog 0-12, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528514</v>
+        <v>528584</v>
       </c>
       <c r="R11" t="n">
-        <v>6454919</v>
+        <v>6454953</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -2067,27 +2051,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>*gnag/kläck</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2107,27 +2086,27 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier.</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.1″N, 15°29′13.4″E</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>tallar</t>
+          <t>granar</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Pinus</t>
+          <t>Picea</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus</t>
+          <t>Horizontal, dead without ground contact # Viss markkontakt. # Picea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2142,6 +2121,163 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122754716</v>
+      </c>
+      <c r="B12" t="n">
+        <v>5173</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Vallsnäs skog 0-13, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>528514</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6454919</v>
+      </c>
+      <c r="S12" t="n">
+        <v>50</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>*gnag/kläck</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Fynd Geo tracker: 58°14′03.8″N, 15°29′10.6″E</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>tallar</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Pinus</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47408-2024 artfynd.xlsx
+++ b/artfynd/A 47408-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122504872</v>
       </c>
       <c r="B2" t="n">
-        <v>90857</v>
+        <v>90960</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>122505603</v>
       </c>
       <c r="B3" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -960,10 +960,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122734520</v>
+        <v>122734365</v>
       </c>
       <c r="B4" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>44</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -1047,22 +1047,22 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>14:30</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Min. 32 rosetter, varav 1 ex blomknopp.</t>
+          <t>Min 44 rosetter. 1 ex noterad blomknopp.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.9″N, 15°29′12.4″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.6″N, 15°29′12.1″E</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1100,10 +1100,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122730998</v>
+        <v>122732619</v>
       </c>
       <c r="B5" t="n">
-        <v>8430</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1112,34 +1112,33 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1184,7 +1183,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1194,12 +1193,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>*kläck</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1208,7 +1202,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1219,27 +1212,27 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′05.4″N, 15°29′14.9″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier.</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>tallar</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Pinus</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Betula</t>
+          <t>Standing dead tree/snags # Mkt grov ved. # Pinus</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1257,10 +1250,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122732619</v>
+        <v>122730998</v>
       </c>
       <c r="B6" t="n">
-        <v>57400</v>
+        <v>8430</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1269,33 +1262,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1340,7 +1334,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1350,7 +1344,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>*kläck</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1359,6 +1358,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1369,27 +1369,27 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier.</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′05.4″N, 15°29′14.9″E</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>tallar</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Pinus</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Mkt grov ved. # Pinus</t>
+          <t>Horizontal, dead with ground contact # Betula</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1410,7 +1410,7 @@
         <v>122757058</v>
       </c>
       <c r="B7" t="n">
-        <v>98345</v>
+        <v>98347</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1543,10 +1543,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122752963</v>
+        <v>122754049</v>
       </c>
       <c r="B8" t="n">
-        <v>98345</v>
+        <v>98347</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1636,12 +1636,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>3 ex</t>
+          <t>Min. 43 ex.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′05.4″N, 15°29′09.1″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker:  58°14′04.7″N, 15°29′09.4″E</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122788467</v>
+        <v>122789055</v>
       </c>
       <c r="B10" t="n">
         <v>98347</v>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1929,12 +1929,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>5 ex.</t>
+          <t>9 ex.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′06.3″N, 15°29′15.3″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58o14 05.6 N, 15o29 14.4 E</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1972,7 +1972,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122730225</v>
+        <v>122754716</v>
       </c>
       <c r="B11" t="n">
         <v>5173</v>
@@ -2017,14 +2017,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-12, Ög</t>
+          <t>Vallsnäs skog 0-13, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528584</v>
+        <v>528514</v>
       </c>
       <c r="R11" t="n">
-        <v>6454953</v>
+        <v>6454919</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -2051,22 +2051,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>*gnag/kläck</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2086,27 +2091,27 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.1″N, 15°29′13.4″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Fynd Geo tracker: 58°14′03.8″N, 15°29′10.6″E</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>granar</t>
+          <t>tallar</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea</t>
+          <t>Pinus</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Viss markkontakt. # Picea</t>
+          <t>Standing dead tree/snags # Pinus</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2124,7 +2129,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122754716</v>
+        <v>122730225</v>
       </c>
       <c r="B12" t="n">
         <v>5173</v>
@@ -2169,14 +2174,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-13, Ög</t>
+          <t>Vallsnäs skog 0-12, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528514</v>
+        <v>528584</v>
       </c>
       <c r="R12" t="n">
-        <v>6454919</v>
+        <v>6454953</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -2203,27 +2208,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>*gnag/kläck</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2243,27 +2243,27 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Fynd Geo tracker: 58°14′03.8″N, 15°29′10.6″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.1″N, 15°29′13.4″E</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>tallar</t>
+          <t>granar</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Pinus</t>
+          <t>Picea</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus</t>
+          <t>Horizontal, dead without ground contact # Viss markkontakt. # Picea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>

--- a/artfynd/A 47408-2024 artfynd.xlsx
+++ b/artfynd/A 47408-2024 artfynd.xlsx
@@ -963,7 +963,7 @@
         <v>122734365</v>
       </c>
       <c r="B4" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1407,10 +1407,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122757058</v>
+        <v>122754049</v>
       </c>
       <c r="B7" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1451,14 +1451,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vallsnäs skog0-1, Ög</t>
+          <t>Vallsnäs skog 0-13, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528577</v>
+        <v>528514</v>
       </c>
       <c r="R7" t="n">
-        <v>6454845</v>
+        <v>6454919</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Min. 13 ex.</t>
+          <t>Min. 43 ex.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker:  58°14′02.9″N, 15°29′11″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker:  58°14′04.7″N, 15°29′09.4″E</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1543,10 +1543,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122754049</v>
+        <v>122757714</v>
       </c>
       <c r="B8" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -1587,14 +1587,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-13, Ög</t>
+          <t>Vallsnäs skog0-1, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528514</v>
+        <v>528577</v>
       </c>
       <c r="R8" t="n">
-        <v>6454919</v>
+        <v>6454845</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1636,12 +1636,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Min. 43 ex.</t>
+          <t>7 ex.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker:  58°14′04.7″N, 15°29′09.4″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′02.1″N, 15°29′12.4″E</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1836,10 +1836,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122789055</v>
+        <v>122789655</v>
       </c>
       <c r="B10" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1929,12 +1929,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>9 ex.</t>
+          <t>Min. 60 exemplar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58o14 05.6 N, 15o29 14.4 E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58o14 04.8 N, 15o29 14.8 E</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1972,7 +1972,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122754716</v>
+        <v>122730225</v>
       </c>
       <c r="B11" t="n">
         <v>5173</v>
@@ -2017,14 +2017,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-13, Ög</t>
+          <t>Vallsnäs skog 0-12, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528514</v>
+        <v>528584</v>
       </c>
       <c r="R11" t="n">
-        <v>6454919</v>
+        <v>6454953</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -2051,27 +2051,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>*gnag/kläck</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2091,27 +2086,27 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Fynd Geo tracker: 58°14′03.8″N, 15°29′10.6″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.1″N, 15°29′13.4″E</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>tallar</t>
+          <t>granar</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Pinus</t>
+          <t>Picea</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus</t>
+          <t>Horizontal, dead without ground contact # Viss markkontakt. # Picea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2129,7 +2124,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122730225</v>
+        <v>122754716</v>
       </c>
       <c r="B12" t="n">
         <v>5173</v>
@@ -2174,14 +2169,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-12, Ög</t>
+          <t>Vallsnäs skog 0-13, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528584</v>
+        <v>528514</v>
       </c>
       <c r="R12" t="n">
-        <v>6454953</v>
+        <v>6454919</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -2208,22 +2203,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>*gnag/kläck</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2243,27 +2243,27 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.1″N, 15°29′13.4″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Fynd Geo tracker: 58°14′03.8″N, 15°29′10.6″E</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>granar</t>
+          <t>tallar</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea</t>
+          <t>Pinus</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Viss markkontakt. # Picea</t>
+          <t>Standing dead tree/snags # Pinus</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>

--- a/artfynd/A 47408-2024 artfynd.xlsx
+++ b/artfynd/A 47408-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122504872</v>
+        <v>122505603</v>
       </c>
       <c r="B2" t="n">
-        <v>90960</v>
+        <v>98355</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -761,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -771,7 +768,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Min. 36 ex.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,22 +793,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Barrdominerat, lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′03.7″N, 15°29′16.5″E</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tallar</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Pinus</t>
+          <t>Barrdominerat, lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′02.6″N, 15°29′17.2″E</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -824,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122505603</v>
+        <v>122504872</v>
       </c>
       <c r="B3" t="n">
-        <v>98347</v>
+        <v>90964</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -836,35 +823,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -907,7 +897,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -917,12 +907,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Min. 36 ex.</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -942,7 +927,22 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Barrdominerat, lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′02.6″N, 15°29′17.2″E</t>
+          <t>Barrdominerat, lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′03.7″N, 15°29′16.5″E</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tallar</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Pinus</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 47408-2024 artfynd.xlsx
+++ b/artfynd/A 47408-2024 artfynd.xlsx
@@ -1100,10 +1100,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122732619</v>
+        <v>122730998</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>8430</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1112,33 +1112,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1183,7 +1184,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1193,7 +1194,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>*kläck</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1202,6 +1208,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1212,27 +1219,27 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier.</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′05.4″N, 15°29′14.9″E</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>tallar</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Pinus</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Mkt grov ved. # Pinus</t>
+          <t>Horizontal, dead with ground contact # Betula</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1250,10 +1257,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122730998</v>
+        <v>122732619</v>
       </c>
       <c r="B6" t="n">
-        <v>8430</v>
+        <v>57494</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1262,34 +1269,33 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1334,7 +1340,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1344,12 +1350,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>*kläck</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1358,7 +1359,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1369,27 +1369,27 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′05.4″N, 15°29′14.9″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier.</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>tallar</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Pinus</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Betula</t>
+          <t>Standing dead tree/snags # Mkt grov ved. # Pinus</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1407,7 +1407,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122754049</v>
+        <v>122757058</v>
       </c>
       <c r="B7" t="n">
         <v>98355</v>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1451,14 +1451,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-13, Ög</t>
+          <t>Vallsnäs skog0-1, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528514</v>
+        <v>528577</v>
       </c>
       <c r="R7" t="n">
-        <v>6454919</v>
+        <v>6454845</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Min. 43 ex.</t>
+          <t>Min. 13 ex.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker:  58°14′04.7″N, 15°29′09.4″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker:  58°14′02.9″N, 15°29′11″E</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1543,10 +1543,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122757714</v>
+        <v>122758132</v>
       </c>
       <c r="B8" t="n">
-        <v>98355</v>
+        <v>8430</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1555,46 +1555,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vallsnäs skog0-1, Ög</t>
+          <t>Vallsnäs skog 0-12, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528577</v>
+        <v>528584</v>
       </c>
       <c r="R8" t="n">
-        <v>6454845</v>
+        <v>6454953</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1626,7 +1627,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1636,12 +1637,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>7 ex.</t>
+          <t>*kläck/luft</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1661,7 +1662,27 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′02.1″N, 15°29′12.4″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.1″N, 15°29′11.2″E</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Betula</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1679,10 +1700,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122758132</v>
+        <v>122754049</v>
       </c>
       <c r="B9" t="n">
-        <v>8430</v>
+        <v>98355</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1691,47 +1712,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-12, Ög</t>
+          <t>Vallsnäs skog 0-13, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528584</v>
+        <v>528514</v>
       </c>
       <c r="R9" t="n">
-        <v>6454953</v>
+        <v>6454919</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1763,7 +1783,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1773,12 +1793,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>*kläck/luft</t>
+          <t>Min. 43 ex.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1798,27 +1818,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.1″N, 15°29′11.2″E</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Betula</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker:  58°14′04.7″N, 15°29′09.4″E</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1836,10 +1836,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122789655</v>
+        <v>122754716</v>
       </c>
       <c r="B10" t="n">
-        <v>98355</v>
+        <v>5173</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1848,46 +1848,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-11, Ög</t>
+          <t>Vallsnäs skog 0-13, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528638</v>
+        <v>528514</v>
       </c>
       <c r="R10" t="n">
-        <v>6454971</v>
+        <v>6454919</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1914,27 +1915,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Min. 60 exemplar.</t>
+          <t>*gnag/kläck</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1954,7 +1955,27 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58o14 04.8 N, 15o29 14.8 E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Fynd Geo tracker: 58°14′03.8″N, 15°29′10.6″E</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>tallar</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Pinus</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1972,10 +1993,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122730225</v>
+        <v>122789055</v>
       </c>
       <c r="B11" t="n">
-        <v>5173</v>
+        <v>98355</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1984,47 +2005,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-12, Ög</t>
+          <t>Vallsnäs skog 0-11, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528584</v>
+        <v>528638</v>
       </c>
       <c r="R11" t="n">
-        <v>6454953</v>
+        <v>6454971</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -2051,22 +2071,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>9 ex.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2086,27 +2111,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.1″N, 15°29′13.4″E</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>granar</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Viss markkontakt. # Picea</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58o14 05.6 N, 15o29 14.4 E</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2124,7 +2129,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122754716</v>
+        <v>122730225</v>
       </c>
       <c r="B12" t="n">
         <v>5173</v>
@@ -2169,14 +2174,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-13, Ög</t>
+          <t>Vallsnäs skog 0-12, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528514</v>
+        <v>528584</v>
       </c>
       <c r="R12" t="n">
-        <v>6454919</v>
+        <v>6454953</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -2203,27 +2208,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>*gnag/kläck</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2243,27 +2243,27 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Fynd Geo tracker: 58°14′03.8″N, 15°29′10.6″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.1″N, 15°29′13.4″E</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>tallar</t>
+          <t>granar</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Pinus</t>
+          <t>Picea</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus</t>
+          <t>Horizontal, dead without ground contact # Viss markkontakt. # Picea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>

--- a/artfynd/A 47408-2024 artfynd.xlsx
+++ b/artfynd/A 47408-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122505603</v>
       </c>
       <c r="B2" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -960,10 +960,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122734365</v>
+        <v>122735204</v>
       </c>
       <c r="B4" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -995,15 +995,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>54</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -1047,7 +1043,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1057,12 +1053,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Min 44 rosetter. 1 ex noterad blomknopp.</t>
+          <t>Min. 54 rosetter.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1082,7 +1078,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.6″N, 15°29′12.1″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′05.2″N, 15°29′12.8″E</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1100,10 +1096,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122730998</v>
+        <v>122732619</v>
       </c>
       <c r="B5" t="n">
-        <v>8430</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1112,34 +1108,33 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1184,7 +1179,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1194,12 +1189,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>*kläck</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1208,7 +1198,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1219,27 +1208,27 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′05.4″N, 15°29′14.9″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier.</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>tallar</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Pinus</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Betula</t>
+          <t>Standing dead tree/snags # Mkt grov ved. # Pinus</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1257,10 +1246,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122732619</v>
+        <v>122730998</v>
       </c>
       <c r="B6" t="n">
-        <v>57494</v>
+        <v>8430</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1269,33 +1258,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1340,7 +1330,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1350,7 +1340,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>*kläck</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1359,6 +1354,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1369,27 +1365,27 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier.</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′05.4″N, 15°29′14.9″E</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>tallar</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Pinus</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Mkt grov ved. # Pinus</t>
+          <t>Horizontal, dead with ground contact # Betula</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1407,10 +1403,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122757058</v>
+        <v>122757714</v>
       </c>
       <c r="B7" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1442,7 +1438,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1490,7 +1486,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1500,12 +1496,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Min. 13 ex.</t>
+          <t>7 ex.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1525,7 +1521,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker:  58°14′02.9″N, 15°29′11″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′02.1″N, 15°29′12.4″E</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1543,10 +1539,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122758132</v>
+        <v>122753380</v>
       </c>
       <c r="B8" t="n">
-        <v>8430</v>
+        <v>98357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1555,47 +1551,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-12, Ög</t>
+          <t>Vallsnäs skog 0-13, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528584</v>
+        <v>528514</v>
       </c>
       <c r="R8" t="n">
-        <v>6454953</v>
+        <v>6454919</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1627,7 +1622,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1637,12 +1632,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>*kläck/luft</t>
+          <t>Min 25 rosetter.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1662,27 +1657,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.1″N, 15°29′11.2″E</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Betula</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker:  58°14′04.3″N, 15°29′09.4″E Detta fynd angränsar till granplantage och kalhygge.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1700,10 +1675,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122754049</v>
+        <v>122758132</v>
       </c>
       <c r="B9" t="n">
-        <v>98355</v>
+        <v>8430</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1712,46 +1687,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-13, Ög</t>
+          <t>Vallsnäs skog 0-12, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528514</v>
+        <v>528584</v>
       </c>
       <c r="R9" t="n">
-        <v>6454919</v>
+        <v>6454953</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1783,7 +1759,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1793,12 +1769,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Min. 43 ex.</t>
+          <t>*kläck/luft</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1818,7 +1794,27 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker:  58°14′04.7″N, 15°29′09.4″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.1″N, 15°29′11.2″E</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Betula</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1836,10 +1832,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122754716</v>
+        <v>122789655</v>
       </c>
       <c r="B10" t="n">
-        <v>5173</v>
+        <v>98357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1848,47 +1844,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-13, Ög</t>
+          <t>Vallsnäs skog 0-11, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528514</v>
+        <v>528638</v>
       </c>
       <c r="R10" t="n">
-        <v>6454919</v>
+        <v>6454971</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1915,27 +1910,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>*gnag/kläck</t>
+          <t>Min. 60 exemplar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1955,27 +1950,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Fynd Geo tracker: 58°14′03.8″N, 15°29′10.6″E</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>tallar</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Pinus</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58o14 04.8 N, 15o29 14.8 E</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1993,10 +1968,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122789055</v>
+        <v>122730225</v>
       </c>
       <c r="B11" t="n">
-        <v>98355</v>
+        <v>5173</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2005,46 +1980,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-11, Ög</t>
+          <t>Vallsnäs skog 0-12, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528638</v>
+        <v>528584</v>
       </c>
       <c r="R11" t="n">
-        <v>6454971</v>
+        <v>6454953</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -2071,27 +2047,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>9 ex.</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2111,7 +2082,27 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58o14 05.6 N, 15o29 14.4 E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.1″N, 15°29′13.4″E</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>granar</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Viss markkontakt. # Picea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2129,7 +2120,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122730225</v>
+        <v>122754716</v>
       </c>
       <c r="B12" t="n">
         <v>5173</v>
@@ -2174,14 +2165,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-12, Ög</t>
+          <t>Vallsnäs skog 0-13, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528584</v>
+        <v>528514</v>
       </c>
       <c r="R12" t="n">
-        <v>6454953</v>
+        <v>6454919</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -2208,22 +2199,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>*gnag/kläck</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2243,27 +2239,27 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.1″N, 15°29′13.4″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Fynd Geo tracker: 58°14′03.8″N, 15°29′10.6″E</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>granar</t>
+          <t>tallar</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea</t>
+          <t>Pinus</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Viss markkontakt. # Picea</t>
+          <t>Standing dead tree/snags # Pinus</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>

--- a/artfynd/A 47408-2024 artfynd.xlsx
+++ b/artfynd/A 47408-2024 artfynd.xlsx
@@ -960,10 +960,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122735204</v>
+        <v>122732619</v>
       </c>
       <c r="B4" t="n">
-        <v>98357</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -972,46 +972,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-12, Ög</t>
+          <t>Vallsnäs skog 0-11, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528584</v>
+        <v>528638</v>
       </c>
       <c r="R4" t="n">
-        <v>6454953</v>
+        <v>6454971</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1053,12 +1053,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:33</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Min. 54 rosetter.</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1067,7 +1062,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1078,7 +1072,27 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′05.2″N, 15°29′12.8″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier.</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tallar</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Mkt grov ved. # Pinus</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1096,10 +1110,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122732619</v>
+        <v>122734365</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>98357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1108,46 +1122,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-11, Ög</t>
+          <t>Vallsnäs skog 0-12, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528638</v>
+        <v>528584</v>
       </c>
       <c r="R5" t="n">
-        <v>6454971</v>
+        <v>6454953</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1179,7 +1197,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1189,7 +1207,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Min 44 rosetter. 1 ex noterad blomknopp.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1198,6 +1221,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1208,27 +1232,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier.</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>tallar</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Pinus</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Mkt grov ved. # Pinus</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.6″N, 15°29′12.1″E</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1403,7 +1407,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122757714</v>
+        <v>122756701</v>
       </c>
       <c r="B7" t="n">
         <v>98357</v>
@@ -1438,7 +1442,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1486,7 +1490,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1496,12 +1500,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>7 ex.</t>
+          <t>Min 17 ex.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1521,7 +1525,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′02.1″N, 15°29′12.4″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker:  58°14′03.3″N, 15°29′11.1″E</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1539,7 +1543,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122753380</v>
+        <v>122754049</v>
       </c>
       <c r="B8" t="n">
         <v>98357</v>
@@ -1574,7 +1578,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -1622,7 +1626,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1632,12 +1636,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Min 25 rosetter.</t>
+          <t>Min. 43 ex.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1657,7 +1661,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker:  58°14′04.3″N, 15°29′09.4″E Detta fynd angränsar till granplantage och kalhygge.</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker:  58°14′04.7″N, 15°29′09.4″E</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1832,10 +1836,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122789655</v>
+        <v>122730225</v>
       </c>
       <c r="B10" t="n">
-        <v>98357</v>
+        <v>5173</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1844,46 +1848,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-11, Ög</t>
+          <t>Vallsnäs skog 0-12, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528638</v>
+        <v>528584</v>
       </c>
       <c r="R10" t="n">
-        <v>6454971</v>
+        <v>6454953</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1910,27 +1915,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:10</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Min. 60 exemplar.</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1950,7 +1950,27 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58o14 04.8 N, 15o29 14.8 E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.1″N, 15°29′13.4″E</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>granar</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Viss markkontakt. # Picea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1968,7 +1988,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122730225</v>
+        <v>122754716</v>
       </c>
       <c r="B11" t="n">
         <v>5173</v>
@@ -2013,14 +2033,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-12, Ög</t>
+          <t>Vallsnäs skog 0-13, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528584</v>
+        <v>528514</v>
       </c>
       <c r="R11" t="n">
-        <v>6454953</v>
+        <v>6454919</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -2047,22 +2067,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>*gnag/kläck</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2082,27 +2107,27 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.1″N, 15°29′13.4″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Fynd Geo tracker: 58°14′03.8″N, 15°29′10.6″E</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>granar</t>
+          <t>tallar</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea</t>
+          <t>Pinus</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Viss markkontakt. # Picea</t>
+          <t>Standing dead tree/snags # Pinus</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2120,10 +2145,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122754716</v>
+        <v>122789055</v>
       </c>
       <c r="B12" t="n">
-        <v>5173</v>
+        <v>98357</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2132,47 +2157,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-13, Ög</t>
+          <t>Vallsnäs skog 0-11, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528514</v>
+        <v>528638</v>
       </c>
       <c r="R12" t="n">
-        <v>6454919</v>
+        <v>6454971</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -2199,27 +2223,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>*gnag/kläck</t>
+          <t>9 ex.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2239,27 +2263,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Fynd Geo tracker: 58°14′03.8″N, 15°29′10.6″E</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>tallar</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Pinus</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58o14 05.6 N, 15o29 14.4 E</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>

--- a/artfynd/A 47408-2024 artfynd.xlsx
+++ b/artfynd/A 47408-2024 artfynd.xlsx
@@ -960,10 +960,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122732619</v>
+        <v>122730998</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>8430</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -972,33 +972,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1043,7 +1044,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1053,7 +1054,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>*kläck</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1062,6 +1068,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1072,27 +1079,27 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier.</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′05.4″N, 15°29′14.9″E</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>tallar</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Pinus</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Mkt grov ved. # Pinus</t>
+          <t>Horizontal, dead with ground contact # Betula</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1110,10 +1117,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122734365</v>
+        <v>122733517</v>
       </c>
       <c r="B5" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1145,15 +1152,11 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>115</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1197,7 +1200,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1207,12 +1210,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Min 44 rosetter. 1 ex noterad blomknopp.</t>
+          <t>Min. 115 rosetter.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1232,7 +1235,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.6″N, 15°29′12.1″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.1″N, 15°29′12.5″E</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1250,10 +1253,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122730998</v>
+        <v>122732619</v>
       </c>
       <c r="B6" t="n">
-        <v>8430</v>
+        <v>57494</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1262,34 +1265,33 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1334,7 +1336,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1344,12 +1346,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>*kläck</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1358,7 +1355,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1369,27 +1365,27 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′05.4″N, 15°29′14.9″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier.</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>tallar</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Pinus</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Betula</t>
+          <t>Standing dead tree/snags # Mkt grov ved. # Pinus</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1407,10 +1403,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122756701</v>
+        <v>122753380</v>
       </c>
       <c r="B7" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1442,7 +1438,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1451,14 +1447,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vallsnäs skog0-1, Ög</t>
+          <t>Vallsnäs skog 0-13, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528577</v>
+        <v>528514</v>
       </c>
       <c r="R7" t="n">
-        <v>6454845</v>
+        <v>6454919</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1490,7 +1486,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1500,12 +1496,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Min 17 ex.</t>
+          <t>Min 25 rosetter.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1525,7 +1521,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker:  58°14′03.3″N, 15°29′11.1″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker:  58°14′04.3″N, 15°29′09.4″E Detta fynd angränsar till granplantage och kalhygge.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1543,10 +1539,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122754049</v>
+        <v>122756701</v>
       </c>
       <c r="B8" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1578,7 +1574,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -1587,14 +1583,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-13, Ög</t>
+          <t>Vallsnäs skog0-1, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528514</v>
+        <v>528577</v>
       </c>
       <c r="R8" t="n">
-        <v>6454919</v>
+        <v>6454845</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1626,7 +1622,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1636,12 +1632,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Min. 43 ex.</t>
+          <t>Min 17 ex.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1661,7 +1657,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker:  58°14′04.7″N, 15°29′09.4″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker:  58°14′03.3″N, 15°29′11.1″E</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1836,10 +1832,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122730225</v>
+        <v>122789655</v>
       </c>
       <c r="B10" t="n">
-        <v>5173</v>
+        <v>98365</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1848,47 +1844,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-12, Ög</t>
+          <t>Vallsnäs skog 0-11, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528584</v>
+        <v>528638</v>
       </c>
       <c r="R10" t="n">
-        <v>6454953</v>
+        <v>6454971</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1915,22 +1910,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Min. 60 exemplar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1950,27 +1950,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.1″N, 15°29′13.4″E</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>granar</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Viss markkontakt. # Picea</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58o14 04.8 N, 15o29 14.8 E</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1988,7 +1968,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122754716</v>
+        <v>122730225</v>
       </c>
       <c r="B11" t="n">
         <v>5173</v>
@@ -2033,14 +2013,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-13, Ög</t>
+          <t>Vallsnäs skog 0-12, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528514</v>
+        <v>528584</v>
       </c>
       <c r="R11" t="n">
-        <v>6454919</v>
+        <v>6454953</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -2067,27 +2047,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>*gnag/kläck</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2107,27 +2082,27 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Fynd Geo tracker: 58°14′03.8″N, 15°29′10.6″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.1″N, 15°29′13.4″E</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>tallar</t>
+          <t>granar</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Pinus</t>
+          <t>Picea</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus</t>
+          <t>Horizontal, dead without ground contact # Viss markkontakt. # Picea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2145,10 +2120,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122789055</v>
+        <v>122754716</v>
       </c>
       <c r="B12" t="n">
-        <v>98357</v>
+        <v>5173</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2157,46 +2132,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-11, Ög</t>
+          <t>Vallsnäs skog 0-13, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528638</v>
+        <v>528514</v>
       </c>
       <c r="R12" t="n">
-        <v>6454971</v>
+        <v>6454919</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -2223,27 +2199,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>9 ex.</t>
+          <t>*gnag/kläck</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2263,7 +2239,27 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58o14 05.6 N, 15o29 14.4 E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Fynd Geo tracker: 58°14′03.8″N, 15°29′10.6″E</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>tallar</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Pinus</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>

--- a/artfynd/A 47408-2024 artfynd.xlsx
+++ b/artfynd/A 47408-2024 artfynd.xlsx
@@ -960,10 +960,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122730998</v>
+        <v>122734520</v>
       </c>
       <c r="B4" t="n">
-        <v>8430</v>
+        <v>98365</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -972,47 +972,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-11, Ög</t>
+          <t>Vallsnäs skog 0-12, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528638</v>
+        <v>528584</v>
       </c>
       <c r="R4" t="n">
-        <v>6454971</v>
+        <v>6454953</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1044,7 +1047,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1054,12 +1057,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>*kläck</t>
+          <t>Min. 32 rosetter, varav 1 ex blomknopp.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1079,27 +1082,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′05.4″N, 15°29′14.9″E</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Betula</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.9″N, 15°29′12.4″E</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1117,10 +1100,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122733517</v>
+        <v>122732619</v>
       </c>
       <c r="B5" t="n">
-        <v>98365</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1129,46 +1112,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-12, Ög</t>
+          <t>Vallsnäs skog 0-11, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528584</v>
+        <v>528638</v>
       </c>
       <c r="R5" t="n">
-        <v>6454953</v>
+        <v>6454971</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1200,7 +1183,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1210,12 +1193,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Min. 115 rosetter.</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1224,7 +1202,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1235,7 +1212,27 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.1″N, 15°29′12.5″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier.</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tallar</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Mkt grov ved. # Pinus</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1253,10 +1250,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122732619</v>
+        <v>122730998</v>
       </c>
       <c r="B6" t="n">
-        <v>57494</v>
+        <v>8430</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1265,33 +1262,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1336,7 +1334,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1346,7 +1344,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>*kläck</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1355,6 +1358,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1365,27 +1369,27 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier.</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′05.4″N, 15°29′14.9″E</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>tallar</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Pinus</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Mkt grov ved. # Pinus</t>
+          <t>Horizontal, dead with ground contact # Betula</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1403,7 +1407,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122753380</v>
+        <v>122753162</v>
       </c>
       <c r="B7" t="n">
         <v>98365</v>
@@ -1438,7 +1442,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1486,7 +1490,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1496,12 +1500,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Min 25 rosetter.</t>
+          <t>4 ex</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1521,7 +1525,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker:  58°14′04.3″N, 15°29′09.4″E Detta fynd angränsar till granplantage och kalhygge.</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.5″N, 15°29′09.3″E</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1539,10 +1543,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122756701</v>
+        <v>122758132</v>
       </c>
       <c r="B8" t="n">
-        <v>98365</v>
+        <v>8430</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1551,46 +1555,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vallsnäs skog0-1, Ög</t>
+          <t>Vallsnäs skog 0-12, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528577</v>
+        <v>528584</v>
       </c>
       <c r="R8" t="n">
-        <v>6454845</v>
+        <v>6454953</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1622,7 +1627,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1632,12 +1637,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Min 17 ex.</t>
+          <t>*kläck/luft</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1657,7 +1662,27 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker:  58°14′03.3″N, 15°29′11.1″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.1″N, 15°29′11.2″E</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Betula</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1675,10 +1700,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122758132</v>
+        <v>122757714</v>
       </c>
       <c r="B9" t="n">
-        <v>8430</v>
+        <v>98365</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1687,47 +1712,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-12, Ög</t>
+          <t>Vallsnäs skog0-1, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528584</v>
+        <v>528577</v>
       </c>
       <c r="R9" t="n">
-        <v>6454953</v>
+        <v>6454845</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1759,7 +1783,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1769,12 +1793,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>*kläck/luft</t>
+          <t>7 ex.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1794,27 +1818,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.1″N, 15°29′11.2″E</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Betula</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′02.1″N, 15°29′12.4″E</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1832,7 +1836,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122789655</v>
+        <v>122789055</v>
       </c>
       <c r="B10" t="n">
         <v>98365</v>
@@ -1867,7 +1871,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -1915,7 +1919,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1925,12 +1929,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Min. 60 exemplar.</t>
+          <t>9 ex.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1950,7 +1954,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58o14 04.8 N, 15o29 14.8 E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58o14 05.6 N, 15o29 14.4 E</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>

--- a/artfynd/A 47408-2024 artfynd.xlsx
+++ b/artfynd/A 47408-2024 artfynd.xlsx
@@ -1972,7 +1972,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122730225</v>
+        <v>122754716</v>
       </c>
       <c r="B11" t="n">
         <v>5173</v>
@@ -2017,14 +2017,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-12, Ög</t>
+          <t>Vallsnäs skog 0-13, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528584</v>
+        <v>528514</v>
       </c>
       <c r="R11" t="n">
-        <v>6454953</v>
+        <v>6454919</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -2051,22 +2051,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>*gnag/kläck</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2086,27 +2091,27 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.1″N, 15°29′13.4″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Fynd Geo tracker: 58°14′03.8″N, 15°29′10.6″E</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>granar</t>
+          <t>tallar</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea</t>
+          <t>Pinus</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Viss markkontakt. # Picea</t>
+          <t>Standing dead tree/snags # Pinus</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2124,7 +2129,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122754716</v>
+        <v>122730225</v>
       </c>
       <c r="B12" t="n">
         <v>5173</v>
@@ -2169,14 +2174,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-13, Ög</t>
+          <t>Vallsnäs skog 0-12, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528514</v>
+        <v>528584</v>
       </c>
       <c r="R12" t="n">
-        <v>6454919</v>
+        <v>6454953</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -2203,27 +2208,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>*gnag/kläck</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2243,27 +2243,27 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Fynd Geo tracker: 58°14′03.8″N, 15°29′10.6″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.1″N, 15°29′13.4″E</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>tallar</t>
+          <t>granar</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Pinus</t>
+          <t>Picea</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus</t>
+          <t>Horizontal, dead without ground contact # Viss markkontakt. # Picea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>

--- a/artfynd/A 47408-2024 artfynd.xlsx
+++ b/artfynd/A 47408-2024 artfynd.xlsx
@@ -1972,7 +1972,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122754716</v>
+        <v>122730225</v>
       </c>
       <c r="B11" t="n">
         <v>5173</v>
@@ -2017,14 +2017,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-13, Ög</t>
+          <t>Vallsnäs skog 0-12, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528514</v>
+        <v>528584</v>
       </c>
       <c r="R11" t="n">
-        <v>6454919</v>
+        <v>6454953</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -2051,27 +2051,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>*gnag/kläck</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2091,27 +2086,27 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Fynd Geo tracker: 58°14′03.8″N, 15°29′10.6″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.1″N, 15°29′13.4″E</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>tallar</t>
+          <t>granar</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Pinus</t>
+          <t>Picea</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus</t>
+          <t>Horizontal, dead without ground contact # Viss markkontakt. # Picea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2129,7 +2124,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122730225</v>
+        <v>122754716</v>
       </c>
       <c r="B12" t="n">
         <v>5173</v>
@@ -2174,14 +2169,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-12, Ög</t>
+          <t>Vallsnäs skog 0-13, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528584</v>
+        <v>528514</v>
       </c>
       <c r="R12" t="n">
-        <v>6454953</v>
+        <v>6454919</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -2208,22 +2203,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>*gnag/kläck</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2243,27 +2243,27 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.1″N, 15°29′13.4″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Fynd Geo tracker: 58°14′03.8″N, 15°29′10.6″E</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>granar</t>
+          <t>tallar</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea</t>
+          <t>Pinus</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Viss markkontakt. # Picea</t>
+          <t>Standing dead tree/snags # Pinus</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>

--- a/artfynd/A 47408-2024 artfynd.xlsx
+++ b/artfynd/A 47408-2024 artfynd.xlsx
@@ -960,7 +960,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122734520</v>
+        <v>122733517</v>
       </c>
       <c r="B4" t="n">
         <v>98365</v>
@@ -995,15 +995,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>115</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -1047,7 +1043,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1057,12 +1053,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Min. 32 rosetter, varav 1 ex blomknopp.</t>
+          <t>Min. 115 rosetter.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1082,7 +1078,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.9″N, 15°29′12.4″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.1″N, 15°29′12.5″E</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1100,10 +1096,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122732619</v>
+        <v>122730998</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>8430</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1112,33 +1108,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1183,7 +1180,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1193,7 +1190,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>*kläck</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1202,6 +1204,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1212,27 +1215,27 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier.</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′05.4″N, 15°29′14.9″E</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>tallar</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Pinus</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Mkt grov ved. # Pinus</t>
+          <t>Horizontal, dead with ground contact # Betula</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1250,10 +1253,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122730998</v>
+        <v>122732619</v>
       </c>
       <c r="B6" t="n">
-        <v>8430</v>
+        <v>57494</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1262,34 +1265,33 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1334,7 +1336,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1344,12 +1346,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>*kläck</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1358,7 +1355,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1369,27 +1365,27 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′05.4″N, 15°29′14.9″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier.</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>tallar</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Pinus</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Betula</t>
+          <t>Standing dead tree/snags # Mkt grov ved. # Pinus</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1407,7 +1403,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122753162</v>
+        <v>122757714</v>
       </c>
       <c r="B7" t="n">
         <v>98365</v>
@@ -1442,7 +1438,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1451,14 +1447,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-13, Ög</t>
+          <t>Vallsnäs skog0-1, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528514</v>
+        <v>528577</v>
       </c>
       <c r="R7" t="n">
-        <v>6454919</v>
+        <v>6454845</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1490,7 +1486,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1500,12 +1496,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>4 ex</t>
+          <t>7 ex.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1525,7 +1521,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.5″N, 15°29′09.3″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′02.1″N, 15°29′12.4″E</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1700,7 +1696,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122757714</v>
+        <v>122753380</v>
       </c>
       <c r="B9" t="n">
         <v>98365</v>
@@ -1735,7 +1731,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -1744,14 +1740,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vallsnäs skog0-1, Ög</t>
+          <t>Vallsnäs skog 0-13, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528577</v>
+        <v>528514</v>
       </c>
       <c r="R9" t="n">
-        <v>6454845</v>
+        <v>6454919</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1783,7 +1779,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1793,12 +1789,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>7 ex.</t>
+          <t>Min 25 rosetter.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1818,7 +1814,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′02.1″N, 15°29′12.4″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker:  58°14′04.3″N, 15°29′09.4″E Detta fynd angränsar till granplantage och kalhygge.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1836,7 +1832,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122789055</v>
+        <v>122789655</v>
       </c>
       <c r="B10" t="n">
         <v>98365</v>
@@ -1871,7 +1867,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -1919,7 +1915,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1929,12 +1925,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>9 ex.</t>
+          <t>Min. 60 exemplar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1954,7 +1950,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58o14 05.6 N, 15o29 14.4 E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58o14 04.8 N, 15o29 14.8 E</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1972,7 +1968,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122730225</v>
+        <v>122754716</v>
       </c>
       <c r="B11" t="n">
         <v>5173</v>
@@ -2017,14 +2013,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-12, Ög</t>
+          <t>Vallsnäs skog 0-13, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528584</v>
+        <v>528514</v>
       </c>
       <c r="R11" t="n">
-        <v>6454953</v>
+        <v>6454919</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -2051,22 +2047,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>*gnag/kläck</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2086,27 +2087,27 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.1″N, 15°29′13.4″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Fynd Geo tracker: 58°14′03.8″N, 15°29′10.6″E</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>granar</t>
+          <t>tallar</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea</t>
+          <t>Pinus</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Viss markkontakt. # Picea</t>
+          <t>Standing dead tree/snags # Pinus</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2124,7 +2125,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122754716</v>
+        <v>122730225</v>
       </c>
       <c r="B12" t="n">
         <v>5173</v>
@@ -2169,14 +2170,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-13, Ög</t>
+          <t>Vallsnäs skog 0-12, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528514</v>
+        <v>528584</v>
       </c>
       <c r="R12" t="n">
-        <v>6454919</v>
+        <v>6454953</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -2203,27 +2204,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>*gnag/kläck</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2243,27 +2239,27 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Fynd Geo tracker: 58°14′03.8″N, 15°29′10.6″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.1″N, 15°29′13.4″E</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>tallar</t>
+          <t>granar</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Pinus</t>
+          <t>Picea</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus</t>
+          <t>Horizontal, dead without ground contact # Viss markkontakt. # Picea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>

--- a/artfynd/A 47408-2024 artfynd.xlsx
+++ b/artfynd/A 47408-2024 artfynd.xlsx
@@ -960,7 +960,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122733517</v>
+        <v>122735204</v>
       </c>
       <c r="B4" t="n">
         <v>98365</v>
@@ -995,7 +995,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>54</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1053,12 +1053,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Min. 115 rosetter.</t>
+          <t>Min. 54 rosetter.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.1″N, 15°29′12.5″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′05.2″N, 15°29′12.8″E</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1096,10 +1096,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122730998</v>
+        <v>122732619</v>
       </c>
       <c r="B5" t="n">
-        <v>8430</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1108,34 +1108,33 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1180,7 +1179,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1190,12 +1189,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>*kläck</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1204,7 +1198,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1215,27 +1208,27 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′05.4″N, 15°29′14.9″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier.</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>tallar</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Pinus</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Betula</t>
+          <t>Standing dead tree/snags # Mkt grov ved. # Pinus</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1253,10 +1246,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122732619</v>
+        <v>122730998</v>
       </c>
       <c r="B6" t="n">
-        <v>57494</v>
+        <v>8430</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1265,33 +1258,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1336,7 +1330,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1346,7 +1340,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>*kläck</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1355,6 +1354,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1365,27 +1365,27 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier.</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′05.4″N, 15°29′14.9″E</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>tallar</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Pinus</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Mkt grov ved. # Pinus</t>
+          <t>Horizontal, dead with ground contact # Betula</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1403,7 +1403,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122757714</v>
+        <v>122757058</v>
       </c>
       <c r="B7" t="n">
         <v>98365</v>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1496,12 +1496,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>7 ex.</t>
+          <t>Min. 13 ex.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′02.1″N, 15°29′12.4″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker:  58°14′02.9″N, 15°29′11″E</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1696,7 +1696,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122753380</v>
+        <v>122754049</v>
       </c>
       <c r="B9" t="n">
         <v>98365</v>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Min 25 rosetter.</t>
+          <t>Min. 43 ex.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker:  58°14′04.3″N, 15°29′09.4″E Detta fynd angränsar till granplantage och kalhygge.</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker:  58°14′04.7″N, 15°29′09.4″E</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 47408-2024 artfynd.xlsx
+++ b/artfynd/A 47408-2024 artfynd.xlsx
@@ -960,10 +960,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122735204</v>
+        <v>122733517</v>
       </c>
       <c r="B4" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>115</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1053,12 +1053,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Min. 54 rosetter.</t>
+          <t>Min. 115 rosetter.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′05.2″N, 15°29′12.8″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.1″N, 15°29′12.5″E</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1099,7 +1099,7 @@
         <v>122732619</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1403,10 +1403,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122757058</v>
+        <v>122752963</v>
       </c>
       <c r="B7" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1447,14 +1447,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vallsnäs skog0-1, Ög</t>
+          <t>Vallsnäs skog 0-13, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528577</v>
+        <v>528514</v>
       </c>
       <c r="R7" t="n">
-        <v>6454845</v>
+        <v>6454919</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1496,12 +1496,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Min. 13 ex.</t>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker:  58°14′02.9″N, 15°29′11″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′05.4″N, 15°29′09.1″E</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1539,10 +1539,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122758132</v>
+        <v>122756701</v>
       </c>
       <c r="B8" t="n">
-        <v>8430</v>
+        <v>98368</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1551,47 +1551,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-12, Ög</t>
+          <t>Vallsnäs skog0-1, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528584</v>
+        <v>528577</v>
       </c>
       <c r="R8" t="n">
-        <v>6454953</v>
+        <v>6454845</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1623,7 +1622,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1633,12 +1632,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>*kläck/luft</t>
+          <t>Min 17 ex.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1658,27 +1657,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.1″N, 15°29′11.2″E</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Betula</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker:  58°14′03.3″N, 15°29′11.1″E</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1696,10 +1675,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122754049</v>
+        <v>122758132</v>
       </c>
       <c r="B9" t="n">
-        <v>98365</v>
+        <v>8430</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1708,46 +1687,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-13, Ög</t>
+          <t>Vallsnäs skog 0-12, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528514</v>
+        <v>528584</v>
       </c>
       <c r="R9" t="n">
-        <v>6454919</v>
+        <v>6454953</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1779,7 +1759,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1789,12 +1769,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Min. 43 ex.</t>
+          <t>*kläck/luft</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1814,7 +1794,27 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker:  58°14′04.7″N, 15°29′09.4″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.1″N, 15°29′11.2″E</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Betula</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1835,7 +1835,7 @@
         <v>122789655</v>
       </c>
       <c r="B10" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122754716</v>
+        <v>122730225</v>
       </c>
       <c r="B11" t="n">
         <v>5173</v>
@@ -2013,14 +2013,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-13, Ög</t>
+          <t>Vallsnäs skog 0-12, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528514</v>
+        <v>528584</v>
       </c>
       <c r="R11" t="n">
-        <v>6454919</v>
+        <v>6454953</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -2047,27 +2047,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>*gnag/kläck</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2087,27 +2082,27 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Fynd Geo tracker: 58°14′03.8″N, 15°29′10.6″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.1″N, 15°29′13.4″E</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>tallar</t>
+          <t>granar</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Pinus</t>
+          <t>Picea</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus</t>
+          <t>Horizontal, dead without ground contact # Viss markkontakt. # Picea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2125,7 +2120,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122730225</v>
+        <v>122754716</v>
       </c>
       <c r="B12" t="n">
         <v>5173</v>
@@ -2170,14 +2165,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-12, Ög</t>
+          <t>Vallsnäs skog 0-13, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528584</v>
+        <v>528514</v>
       </c>
       <c r="R12" t="n">
-        <v>6454953</v>
+        <v>6454919</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -2204,22 +2199,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>*gnag/kläck</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2239,27 +2239,27 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.1″N, 15°29′13.4″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Fynd Geo tracker: 58°14′03.8″N, 15°29′10.6″E</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>granar</t>
+          <t>tallar</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea</t>
+          <t>Pinus</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Viss markkontakt. # Picea</t>
+          <t>Standing dead tree/snags # Pinus</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>

--- a/artfynd/A 47408-2024 artfynd.xlsx
+++ b/artfynd/A 47408-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -960,10 +960,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122733517</v>
+        <v>122734365</v>
       </c>
       <c r="B4" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -995,11 +995,15 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>44</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -1043,7 +1047,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1053,12 +1057,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Min. 115 rosetter.</t>
+          <t>Min 44 rosetter. 1 ex noterad blomknopp.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1078,7 +1082,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.1″N, 15°29′12.5″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.6″N, 15°29′12.1″E</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1096,10 +1100,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122732619</v>
+        <v>122730998</v>
       </c>
       <c r="B5" t="n">
-        <v>57497</v>
+        <v>8430</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1108,33 +1112,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1179,7 +1184,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1189,7 +1194,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>*kläck</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1198,6 +1208,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1208,27 +1219,27 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier.</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′05.4″N, 15°29′14.9″E</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>tallar</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Pinus</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Mkt grov ved. # Pinus</t>
+          <t>Horizontal, dead with ground contact # Betula</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1246,10 +1257,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122730998</v>
+        <v>122732619</v>
       </c>
       <c r="B6" t="n">
-        <v>8430</v>
+        <v>57497</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1258,34 +1269,33 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1330,7 +1340,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1340,12 +1350,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>*kläck</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1354,7 +1359,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1365,27 +1369,27 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′05.4″N, 15°29′14.9″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier.</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>tallar</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Pinus</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Betula</t>
+          <t>Standing dead tree/snags # Mkt grov ved. # Pinus</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1403,10 +1407,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122752963</v>
+        <v>122756701</v>
       </c>
       <c r="B7" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1438,7 +1442,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1447,14 +1451,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-13, Ög</t>
+          <t>Vallsnäs skog0-1, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528514</v>
+        <v>528577</v>
       </c>
       <c r="R7" t="n">
-        <v>6454919</v>
+        <v>6454845</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1486,7 +1490,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1496,12 +1500,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>3 ex</t>
+          <t>Min 17 ex.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1521,7 +1525,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′05.4″N, 15°29′09.1″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker:  58°14′03.3″N, 15°29′11.1″E</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1539,10 +1543,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122756701</v>
+        <v>122752963</v>
       </c>
       <c r="B8" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1574,7 +1578,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -1583,14 +1587,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vallsnäs skog0-1, Ög</t>
+          <t>Vallsnäs skog 0-13, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528577</v>
+        <v>528514</v>
       </c>
       <c r="R8" t="n">
-        <v>6454845</v>
+        <v>6454919</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1622,7 +1626,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1632,12 +1636,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Min 17 ex.</t>
+          <t>3 ex</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1657,7 +1661,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker:  58°14′03.3″N, 15°29′11.1″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′05.4″N, 15°29′09.1″E</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1835,7 +1839,7 @@
         <v>122789655</v>
       </c>
       <c r="B10" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1968,7 +1972,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122730225</v>
+        <v>122754716</v>
       </c>
       <c r="B11" t="n">
         <v>5173</v>
@@ -2013,14 +2017,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-12, Ög</t>
+          <t>Vallsnäs skog 0-13, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528584</v>
+        <v>528514</v>
       </c>
       <c r="R11" t="n">
-        <v>6454953</v>
+        <v>6454919</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -2047,22 +2051,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>*gnag/kläck</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2082,27 +2091,27 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.1″N, 15°29′13.4″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Fynd Geo tracker: 58°14′03.8″N, 15°29′10.6″E</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>granar</t>
+          <t>tallar</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea</t>
+          <t>Pinus</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Viss markkontakt. # Picea</t>
+          <t>Standing dead tree/snags # Pinus</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2120,7 +2129,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122754716</v>
+        <v>122730225</v>
       </c>
       <c r="B12" t="n">
         <v>5173</v>
@@ -2165,14 +2174,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-13, Ög</t>
+          <t>Vallsnäs skog 0-12, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528514</v>
+        <v>528584</v>
       </c>
       <c r="R12" t="n">
-        <v>6454919</v>
+        <v>6454953</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -2199,27 +2208,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>*gnag/kläck</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2239,27 +2243,27 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Fynd Geo tracker: 58°14′03.8″N, 15°29′10.6″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.1″N, 15°29′13.4″E</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>tallar</t>
+          <t>granar</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Pinus</t>
+          <t>Picea</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus</t>
+          <t>Horizontal, dead without ground contact # Viss markkontakt. # Picea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2274,6 +2278,158 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123429869</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5193</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Vallsnäs skog 0-11, Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>528638</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6454971</v>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Nykil</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Barrdominerat  Fynd lokaliserat på relativt skuggigt läge</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47408-2024 artfynd.xlsx
+++ b/artfynd/A 47408-2024 artfynd.xlsx
@@ -1839,7 +1839,7 @@
         <v>122789655</v>
       </c>
       <c r="B10" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122754716</v>
+        <v>122730225</v>
       </c>
       <c r="B11" t="n">
         <v>5173</v>
@@ -2017,14 +2017,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-13, Ög</t>
+          <t>Vallsnäs skog 0-12, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528514</v>
+        <v>528584</v>
       </c>
       <c r="R11" t="n">
-        <v>6454919</v>
+        <v>6454953</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -2051,27 +2051,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>*gnag/kläck</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2091,27 +2086,27 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Fynd Geo tracker: 58°14′03.8″N, 15°29′10.6″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.1″N, 15°29′13.4″E</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>tallar</t>
+          <t>granar</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Pinus</t>
+          <t>Picea</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus</t>
+          <t>Horizontal, dead without ground contact # Viss markkontakt. # Picea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2129,7 +2124,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122730225</v>
+        <v>122754716</v>
       </c>
       <c r="B12" t="n">
         <v>5173</v>
@@ -2174,14 +2169,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-12, Ög</t>
+          <t>Vallsnäs skog 0-13, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528584</v>
+        <v>528514</v>
       </c>
       <c r="R12" t="n">
-        <v>6454953</v>
+        <v>6454919</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -2208,22 +2203,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>*gnag/kläck</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2243,27 +2243,27 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58°14′04.1″N, 15°29′13.4″E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Fynd Geo tracker: 58°14′03.8″N, 15°29′10.6″E</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>granar</t>
+          <t>tallar</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea</t>
+          <t>Pinus</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Viss markkontakt. # Picea</t>
+          <t>Standing dead tree/snags # Pinus</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>

--- a/artfynd/A 47408-2024 artfynd.xlsx
+++ b/artfynd/A 47408-2024 artfynd.xlsx
@@ -1836,10 +1836,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122789655</v>
+        <v>122754716</v>
       </c>
       <c r="B10" t="n">
-        <v>98376</v>
+        <v>5173</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1848,46 +1848,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-11, Ög</t>
+          <t>Vallsnäs skog 0-13, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528638</v>
+        <v>528514</v>
       </c>
       <c r="R10" t="n">
-        <v>6454971</v>
+        <v>6454919</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1914,27 +1915,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Min. 60 exemplar.</t>
+          <t>*gnag/kläck</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1954,7 +1955,27 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58o14 04.8 N, 15o29 14.8 E</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Fynd Geo tracker: 58°14′03.8″N, 15°29′10.6″E</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>tallar</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Pinus</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2124,10 +2145,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122754716</v>
+        <v>122789055</v>
       </c>
       <c r="B12" t="n">
-        <v>5173</v>
+        <v>98379</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2136,47 +2157,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vallsnäs skog 0-13, Ög</t>
+          <t>Vallsnäs skog 0-11, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528514</v>
+        <v>528638</v>
       </c>
       <c r="R12" t="n">
-        <v>6454919</v>
+        <v>6454971</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -2203,27 +2223,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>*gnag/kläck</t>
+          <t>9 ex.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2243,27 +2263,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Fynd Geo tracker: 58°14′03.8″N, 15°29′10.6″E</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>tallar</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Pinus</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus</t>
+          <t>Barrdominerat, mindre lövinslag. Förekomst av lågor, död ved i olika nedbrytningsstadier. Koordinater fynd Geo tracker: 58o14 05.6 N, 15o29 14.4 E</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>

--- a/artfynd/A 47408-2024 artfynd.xlsx
+++ b/artfynd/A 47408-2024 artfynd.xlsx
@@ -2284,7 +2284,7 @@
         <v>123429869</v>
       </c>
       <c r="B13" t="n">
-        <v>5193</v>
+        <v>5194</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>123570434</v>
       </c>
       <c r="B14" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 47408-2024 artfynd.xlsx
+++ b/artfynd/A 47408-2024 artfynd.xlsx
@@ -2284,7 +2284,7 @@
         <v>123429869</v>
       </c>
       <c r="B13" t="n">
-        <v>5194</v>
+        <v>5196</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>123570434</v>
       </c>
       <c r="B14" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 47408-2024 artfynd.xlsx
+++ b/artfynd/A 47408-2024 artfynd.xlsx
@@ -2436,7 +2436,7 @@
         <v>123570434</v>
       </c>
       <c r="B14" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 47408-2024 artfynd.xlsx
+++ b/artfynd/A 47408-2024 artfynd.xlsx
@@ -2436,7 +2436,7 @@
         <v>123570434</v>
       </c>
       <c r="B14" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
